--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.927353459546202</v>
+        <v>0.3131949371762578</v>
       </c>
       <c r="D2" t="n">
-        <v>10.89126208135892</v>
+        <v>1.769830088220824</v>
       </c>
       <c r="E2" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F2" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.51593446444475</v>
+        <v>7.883839350472273</v>
       </c>
       <c r="D3" t="n">
-        <v>47.55302314343119</v>
+        <v>7.727366260807568</v>
       </c>
       <c r="E3" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F3" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.67716910578243</v>
+        <v>4.010039979689646</v>
       </c>
       <c r="D4" t="n">
-        <v>32.46852741178581</v>
+        <v>5.276135704415195</v>
       </c>
       <c r="E4" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F4" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.22627242107537</v>
+        <v>8.974269268424749</v>
       </c>
       <c r="D5" t="n">
-        <v>52.29388706790535</v>
+        <v>8.497756648534619</v>
       </c>
       <c r="E5" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F5" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.19033823669427</v>
+        <v>7.343429963462818</v>
       </c>
       <c r="D6" t="n">
-        <v>50.62705220677015</v>
+        <v>8.22689598360015</v>
       </c>
       <c r="E6" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F6" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.97402768907292</v>
+        <v>3.40827949947435</v>
       </c>
       <c r="D7" t="n">
-        <v>13.4603267456407</v>
+        <v>2.187303096166614</v>
       </c>
       <c r="E7" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F7" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.42575025651156</v>
+        <v>5.431684416683128</v>
       </c>
       <c r="D8" t="n">
-        <v>27.7247610819605</v>
+        <v>4.505273675818581</v>
       </c>
       <c r="E8" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F8" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>59.84575816512366</v>
+        <v>9.724935701832596</v>
       </c>
       <c r="D9" t="n">
-        <v>55.84809325222245</v>
+        <v>9.075315153486148</v>
       </c>
       <c r="E9" t="n">
-        <v>18.37301623279619</v>
+        <v>2.98561513782938</v>
       </c>
       <c r="F9" t="n">
-        <v>16.67809048017084</v>
+        <v>2.710189703027762</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
